--- a/tools/importer/reports/import-customer-stories.report.xlsx
+++ b/tools/importer/reports/import-customer-stories.report.xlsx
@@ -52,7 +52,7 @@
     <t>customer-stories</t>
   </si>
   <si>
-    <t>2026-08-27T16:13:39.879Z</t>
+    <t>2026-08-27T16:17:59.540Z</t>
   </si>
   <si>
     <t>PwC</t>

--- a/tools/importer/reports/import-customer-stories.report.xlsx
+++ b/tools/importer/reports/import-customer-stories.report.xlsx
@@ -52,7 +52,7 @@
     <t>customer-stories</t>
   </si>
   <si>
-    <t>2026-08-27T16:17:59.540Z</t>
+    <t>2026-08-27T16:42:26.753Z</t>
   </si>
   <si>
     <t>PwC</t>
